--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131288327</v>
       </c>
       <c r="B2" t="n">
-        <v>58041</v>
+        <v>58043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,6 +791,351 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131402104</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Linneröds naturreservat, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>394444</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6225692</v>
+      </c>
+      <c r="S3" t="n">
+        <v>88</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vedby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131402108</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Linneröds naturreservat, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>394444</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6225692</v>
+      </c>
+      <c r="S4" t="n">
+        <v>88</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vedby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131402102</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57880</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Linneröds naturreservat, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>394444</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6225692</v>
+      </c>
+      <c r="S5" t="n">
+        <v>88</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vedby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131288327</v>
       </c>
       <c r="B2" t="n">
-        <v>58043</v>
+        <v>58044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>131402104</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131402108</v>
       </c>
       <c r="B4" t="n">
-        <v>58043</v>
+        <v>58044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>131402102</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131288327</v>
       </c>
       <c r="B2" t="n">
-        <v>58044</v>
+        <v>58045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>131402104</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131402108</v>
       </c>
       <c r="B4" t="n">
-        <v>58044</v>
+        <v>58045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>131402102</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>57882</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131288327</v>
       </c>
       <c r="B2" t="n">
-        <v>58045</v>
+        <v>58048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>131402104</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131402108</v>
       </c>
       <c r="B4" t="n">
-        <v>58045</v>
+        <v>58048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>131402102</v>
       </c>
       <c r="B5" t="n">
-        <v>57882</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131288327</v>
       </c>
       <c r="B2" t="n">
-        <v>58048</v>
+        <v>58049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>131402104</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131402108</v>
       </c>
       <c r="B4" t="n">
-        <v>58048</v>
+        <v>58049</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>131402102</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94174144</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92445186</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,8 +1045,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131288327</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>